--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.51337900675468</v>
+        <v>3.008424088597636</v>
       </c>
       <c r="D2" t="n">
-        <v>19.38466649617829</v>
+        <v>3.150008305628972</v>
       </c>
       <c r="E2" t="n">
-        <v>10.52192280692733</v>
+        <v>1.709812456125692</v>
       </c>
       <c r="F2" t="n">
-        <v>10.16272193930369</v>
+        <v>1.651442315136849</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.96198313394572</v>
+        <v>4.05632225926618</v>
       </c>
       <c r="D3" t="n">
-        <v>31.29917251595728</v>
+        <v>5.086115533843058</v>
       </c>
       <c r="E3" t="n">
-        <v>10.52192280692733</v>
+        <v>1.709812456125692</v>
       </c>
       <c r="F3" t="n">
-        <v>10.16272193930369</v>
+        <v>1.651442315136849</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.55584836339453</v>
+        <v>5.615325359051612</v>
       </c>
       <c r="D4" t="n">
-        <v>43.98348884630171</v>
+        <v>7.147316937524028</v>
       </c>
       <c r="E4" t="n">
-        <v>10.52192280692733</v>
+        <v>1.709812456125692</v>
       </c>
       <c r="F4" t="n">
-        <v>10.16272193930369</v>
+        <v>1.651442315136849</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.6123627466786</v>
+        <v>6.274508946335272</v>
       </c>
       <c r="D5" t="n">
-        <v>34.56529271317864</v>
+        <v>5.61686006589153</v>
       </c>
       <c r="E5" t="n">
-        <v>10.52192280692733</v>
+        <v>1.709812456125692</v>
       </c>
       <c r="F5" t="n">
-        <v>10.16272193930369</v>
+        <v>1.651442315136849</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.5096774136046</v>
+        <v>3.170322579710748</v>
       </c>
       <c r="D6" t="n">
-        <v>18.19437101456064</v>
+        <v>2.956585289866104</v>
       </c>
       <c r="E6" t="n">
-        <v>10.52192280692733</v>
+        <v>1.709812456125692</v>
       </c>
       <c r="F6" t="n">
-        <v>10.16272193930369</v>
+        <v>1.651442315136849</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.45836847138823</v>
+        <v>8.199484876600588</v>
       </c>
       <c r="D7" t="n">
-        <v>47.57743062500965</v>
+        <v>7.731332476564069</v>
       </c>
       <c r="E7" t="n">
-        <v>10.52192280692733</v>
+        <v>1.709812456125692</v>
       </c>
       <c r="F7" t="n">
-        <v>10.16272193930369</v>
+        <v>1.651442315136849</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.74047455248808</v>
+        <v>3.857827114779313</v>
       </c>
       <c r="D8" t="n">
-        <v>24.79705418706707</v>
+        <v>4.029521305398399</v>
       </c>
       <c r="E8" t="n">
-        <v>10.52192280692733</v>
+        <v>1.709812456125692</v>
       </c>
       <c r="F8" t="n">
-        <v>10.16272193930369</v>
+        <v>1.651442315136849</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.38650930051368</v>
+        <v>3.475307761333473</v>
       </c>
       <c r="D9" t="n">
-        <v>25.18420657455214</v>
+        <v>4.092433568364723</v>
       </c>
       <c r="E9" t="n">
-        <v>10.52192280692733</v>
+        <v>1.709812456125692</v>
       </c>
       <c r="F9" t="n">
-        <v>10.16272193930369</v>
+        <v>1.651442315136849</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
